--- a/www/terminologies/ASS-A20-RolePriseCharge-GenreActivite.xlsx
+++ b/www/terminologies/ASS-A20-RolePriseCharge-GenreActivite.xlsx
@@ -99,7 +99,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge|20251222120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge|20260202120000</t>
   </si>
   <si>
     <t/>

--- a/www/terminologies/ASS-A20-RolePriseCharge-GenreActivite.xlsx
+++ b/www/terminologies/ASS-A20-RolePriseCharge-GenreActivite.xlsx
@@ -99,13 +99,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge|20260202120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R22-GenreActivite/FHIR/TRE-R22-GenreActivite|20240329120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R22-GenreActivite/FHIR/TRE-R22-GenreActivite</t>
   </si>
   <si>
     <t>312</t>
